--- a/NOFS-Telescopes.xlsx
+++ b/NOFS-Telescopes.xlsx
@@ -1,20 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10201"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bob.zavala/Desktop/bobMacBackUp/Optics/Ray tracing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C424133-EEA2-5446-91D9-80EAE95100EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED22D768-37AF-3C4B-A1DE-8F835DBC8F70}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15580" yWindow="1440" windowWidth="44560" windowHeight="25060" activeTab="1" xr2:uid="{9120E6CE-487D-4A4E-A0CB-02EC34448099}"/>
+    <workbookView xWindow="50300" yWindow="4000" windowWidth="17800" windowHeight="12860" activeTab="1" xr2:uid="{9120E6CE-487D-4A4E-A0CB-02EC34448099}"/>
   </bookViews>
   <sheets>
     <sheet name="NOFS" sheetId="2" r:id="rId1"/>
-    <sheet name="Exact trace" sheetId="3" r:id="rId2"/>
+    <sheet name="Filter glass" sheetId="4" r:id="rId2"/>
+    <sheet name="40 cm Exact Ray Trace" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -237,6 +238,24 @@
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={303AE714-7CBE-334B-A645-98D535E2AC2B}</author>
+  </authors>
+  <commentList>
+    <comment ref="A1" authorId="0" shapeId="0" xr:uid="{303AE714-7CBE-334B-A645-98D535E2AC2B}">
+      <text>
+        <t xml:space="preserve">[Threaded comment]
+Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
+Comment:
+    Using us.shop.schott.com/ and Doi et al. 2010 AJ, 139, 1628 to match glass to filters for SDSS. </t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={164D0010-E569-924F-BA13-1C3EDB91DED7}</author>
   </authors>
   <commentList>
@@ -253,7 +272,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="127">
   <si>
     <t>Diam. (mm)</t>
   </si>
@@ -2420,6 +2439,375 @@
   </si>
   <si>
     <t>40cm</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> P - V</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">at         </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> α</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>C</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> P - V at</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">   α</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">P - V </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">at </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> α</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nm)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>W</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">C </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>rms</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t xml:space="preserve">at   </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> α</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (nm)</t>
+    </r>
+  </si>
+  <si>
+    <t>Filter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">glass </t>
+  </si>
+  <si>
+    <t>SDSS u</t>
+  </si>
+  <si>
+    <t>SDSS g</t>
+  </si>
+  <si>
+    <t>SDSS r</t>
+  </si>
+  <si>
+    <t>SDSS i</t>
+  </si>
+  <si>
+    <t>SDSS z</t>
+  </si>
+  <si>
+    <t>BG38/UG11</t>
+  </si>
+  <si>
+    <t>GG400</t>
+  </si>
+  <si>
+    <t>OG550</t>
+  </si>
+  <si>
+    <t>RG695</t>
+  </si>
+  <si>
+    <t>RG830</t>
+  </si>
+  <si>
+    <r>
+      <t>n</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <vertAlign val="subscript"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow (Body)"/>
+      </rPr>
+      <t>d</t>
+    </r>
+  </si>
+  <si>
+    <t>1.527/1.563</t>
+  </si>
+  <si>
+    <t>Offset from SDSS r                    (5 mm filters) (mm)</t>
+  </si>
+  <si>
+    <t>Offset from SDSS r                    (7.5 mm filters) (mm)</t>
   </si>
 </sst>
 </file>
@@ -2434,7 +2822,7 @@
     <numFmt numFmtId="168" formatCode="0.0000E+00"/>
     <numFmt numFmtId="169" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2522,6 +2910,12 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2543,7 +2937,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2606,6 +3000,12 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -3151,6 +3551,14 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="A1" dT="2026-02-09T21:43:15.80" personId="{8C851638-141B-034A-B4A3-8E6355A961FE}" id="{303AE714-7CBE-334B-A645-98D535E2AC2B}">
+    <text xml:space="preserve">Using us.shop.schott.com/ and Doi et al. 2010 AJ, 139, 1628 to match glass to filters for SDSS. </text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment3.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="N3" dT="2026-01-22T00:16:24.58" personId="{8C851638-141B-034A-B4A3-8E6355A961FE}" id="{164D0010-E569-924F-BA13-1C3EDB91DED7}">
     <text>1215 mm is the focal plane location via a paraxial y-nu ray trace. Using the 1:5.3 scale drawing the focus via the back focal length to presumed secondary mirror surface is 1220  mm.</text>
   </threadedComment>
@@ -3313,7 +3721,7 @@
         <v>4</v>
       </c>
       <c r="D4" s="5">
-        <v>-6060.69</v>
+        <v>-6061.4560000000001</v>
       </c>
       <c r="E4" s="1">
         <v>-1.637</v>
@@ -3376,7 +3784,7 @@
         <v>-885</v>
       </c>
       <c r="G5" s="1">
-        <f>2*C15</f>
+        <f>C15*2</f>
         <v>-2865.12</v>
       </c>
       <c r="H5" s="1">
@@ -3468,7 +3876,7 @@
       </c>
       <c r="B9">
         <f>D4/2</f>
-        <v>-3030.3449999999998</v>
+        <v>-3030.7280000000001</v>
       </c>
       <c r="C9">
         <f>G4/2</f>
@@ -3476,46 +3884,46 @@
       </c>
       <c r="D9">
         <f>B9/B4</f>
-        <v>-2.3531542654801285</v>
+        <v>-2.3534516765285995</v>
       </c>
       <c r="E9" s="6">
         <f>B4/(2048*(D9^3))</f>
-        <v>-4.8257022975322E-2</v>
+        <v>-4.8238730237507924E-2</v>
       </c>
       <c r="F9" s="7">
         <f>ABS(C4/D9)</f>
-        <v>1.6998460571321088</v>
+        <v>1.6996312437143815</v>
       </c>
       <c r="G9" s="7">
         <f>ABS((I4+K4+N4+Q4+T4+W4)/(B9-F4))</f>
-        <v>1.6716506525943573</v>
+        <v>1.6711564852678069</v>
       </c>
       <c r="H9" s="8">
         <f>AVERAGE(F9,G9)</f>
-        <v>1.685748354863233</v>
+        <v>1.6853938644910942</v>
       </c>
       <c r="I9" s="8">
         <f>-1*(I4+K4+N4+Q4+T4+W4+F4)/B9</f>
-        <v>0.14190364463452176</v>
+        <v>0.1418857119477564</v>
       </c>
       <c r="J9" s="8">
         <f>ABS(G4/D4)</f>
-        <v>1</v>
+        <v>0.99987362772244814</v>
       </c>
       <c r="K9" s="8">
         <f>J9*(H9-1)/H9</f>
-        <v>0.40679165006147594</v>
+        <v>0.40661548860826513</v>
       </c>
       <c r="L9" s="8">
         <f>-1-2*(1+I9)/(H9^2*(H9-I9))</f>
-        <v>-1.5205594701159819</v>
+        <v>-1.5208838467183601</v>
       </c>
       <c r="M9" s="5">
         <v>-1</v>
       </c>
       <c r="N9">
         <f>-1*(((H9+1)/(H9-1))^2)-2*H9*(H9+1)/((H9-I9)*(H9-1)^3)</f>
-        <v>-33.527359469746898</v>
+        <v>-33.565149404527993</v>
       </c>
       <c r="O9" s="1">
         <v>3.504</v>
@@ -3528,15 +3936,15 @@
       </c>
       <c r="R9" s="8">
         <f>(-1*($H$9^2+$I$9)*((O9*0.0175/60)*$B$4)^2)/(8*(1+$I$9)*$H$9*$B$4*$C$4)*1000000</f>
-        <v>-65.150736710657966</v>
+        <v>-65.138971000744334</v>
       </c>
       <c r="S9" s="8">
         <f>(-1*($H$9^2+$I$9)*((P9*0.0175/60)*$B$4)^2)/(8*(1+$I$9)*$H$9*$B$4*$C$4)*1000000</f>
-        <v>-260.60294684263187</v>
+        <v>-260.55588400297734</v>
       </c>
       <c r="T9" s="8">
         <f>(-1*($H$9^2+$I$9)*((Q9*0.0175/60)*$B$4)^2)/(8*(1+$I$9)*$H$9*$B$4*$C$4)*1000000</f>
-        <v>-586.13353265975127</v>
+        <v>-586.02768156022273</v>
       </c>
       <c r="U9" s="8">
         <f>(O9*0.0175/60)*$B$4/(48*$C$4^2)*1000000</f>
@@ -3579,15 +3987,15 @@
       </c>
       <c r="R11" s="5">
         <f>R9/SQRT(24)</f>
-        <v>-13.298838442293679</v>
+        <v>-13.296436776814513</v>
       </c>
       <c r="S11" s="5">
         <f>S9/SQRT(24)</f>
-        <v>-53.195353769174716</v>
+        <v>-53.185747107258052</v>
       </c>
       <c r="T11" s="5">
         <f>T9/SQRT(24)</f>
-        <v>-119.64400634594415</v>
+        <v>-119.62239958073103</v>
       </c>
       <c r="U11" s="5">
         <f>U9/32</f>
@@ -3768,13 +4176,13 @@
         <v>38</v>
       </c>
       <c r="P14" s="10" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>49</v>
+        <v>108</v>
       </c>
       <c r="R14" s="10" t="s">
-        <v>48</v>
+        <v>109</v>
       </c>
       <c r="S14" s="10" t="s">
         <v>47</v>
@@ -3783,7 +4191,7 @@
         <v>49</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>48</v>
+        <v>110</v>
       </c>
       <c r="V14" s="9" t="s">
         <v>65</v>
@@ -3877,6 +4285,130 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26631ECC-334B-4D45-903B-E58ADFB43918}">
+  <dimension ref="A1:E6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="3" max="3" width="10.83203125" style="7"/>
+    <col min="4" max="4" width="14.5" style="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" s="2" customFormat="1" ht="69" x14ac:dyDescent="0.25">
+      <c r="A1" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>123</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>125</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>113</v>
+      </c>
+      <c r="B2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D2" s="23" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>114</v>
+      </c>
+      <c r="B3" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="7">
+        <v>1.52</v>
+      </c>
+      <c r="D3" s="7">
+        <f>5*((C3-$C$4)/(C3*$C$4))</f>
+        <v>1.7404622667780579E-2</v>
+      </c>
+      <c r="E3" s="7">
+        <f>7.5*((C3-$C$4)/(C3*$C$4))</f>
+        <v>2.610693400167087E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C4" s="7">
+        <v>1.512</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0</v>
+      </c>
+      <c r="E4" s="7">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>116</v>
+      </c>
+      <c r="B5" t="s">
+        <v>121</v>
+      </c>
+      <c r="C5" s="7">
+        <v>1.5329999999999999</v>
+      </c>
+      <c r="D5" s="7">
+        <f>5*((C5-$C$4)/(C5*$C$4))</f>
+        <v>4.5299702833949212E-2</v>
+      </c>
+      <c r="E5" s="7">
+        <f>7.5*((C5-$C$4)/(C5*$C$4))</f>
+        <v>6.7949554250923819E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>117</v>
+      </c>
+      <c r="B6" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="7">
+        <v>1.56</v>
+      </c>
+      <c r="D6" s="7">
+        <f>5*((C6-$C$4)/(C6*$C$4))</f>
+        <v>0.10175010175010185</v>
+      </c>
+      <c r="E6" s="7">
+        <f>7.5*((C6-$C$4)/(C6*$C$4))</f>
+        <v>0.15262515262515278</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1E3D5ED7-AD07-A046-96A1-F16751D23497}">
   <dimension ref="A1:N28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
